--- a/artfynd/A 32139-2026 artfynd.xlsx
+++ b/artfynd/A 32139-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136006172</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>136006175</v>
       </c>
       <c r="B3" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>136006183</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136006174</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136006176</v>
       </c>
       <c r="B6" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136006180</v>
       </c>
       <c r="B7" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>136006182</v>
       </c>
       <c r="B8" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>136006173</v>
       </c>
       <c r="B9" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>136004832</v>
       </c>
       <c r="B14" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>136006178</v>
       </c>
       <c r="B15" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>136006179</v>
       </c>
       <c r="B16" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136006189</v>
       </c>
       <c r="B17" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
